--- a/data/b_Optimierung/Verfügbarkeiten_Solarthermie_täglich_2023.xlsx
+++ b/data/b_Optimierung/Verfügbarkeiten_Solarthermie_täglich_2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HansisRasanterRaser\Desktop\UNI\000_DA\git\knEBiD\data\b_Optimierung\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B3905E-4CD5-49C5-A3A4-16943DBD3199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F814B6-F823-45A7-B7C4-C41F078AC848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Datum</t>
   </si>
@@ -29,6 +29,12 @@
   </si>
   <si>
     <t>Anderee</t>
+  </si>
+  <si>
+    <t>Flächengeothermie</t>
+  </si>
+  <si>
+    <t>Tiefengeothermie</t>
   </si>
 </sst>
 </file>
@@ -87,12 +93,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -397,21 +406,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C366"/>
+  <dimension ref="A1:E366"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="25.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>44927</v>
       </c>
@@ -421,8 +442,14 @@
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>44928</v>
       </c>
@@ -432,8 +459,14 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>44929</v>
       </c>
@@ -443,8 +476,14 @@
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>44930</v>
       </c>
@@ -454,8 +493,14 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>44931</v>
       </c>
@@ -465,8 +510,14 @@
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>44932</v>
       </c>
@@ -476,8 +527,14 @@
       <c r="C7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>44933</v>
       </c>
@@ -487,8 +544,14 @@
       <c r="C8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>44934</v>
       </c>
@@ -498,8 +561,14 @@
       <c r="C9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>44935</v>
       </c>
@@ -509,8 +578,14 @@
       <c r="C10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>44936</v>
       </c>
@@ -520,8 +595,14 @@
       <c r="C11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>44937</v>
       </c>
@@ -531,8 +612,14 @@
       <c r="C12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>44938</v>
       </c>
@@ -542,8 +629,14 @@
       <c r="C13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>44939</v>
       </c>
@@ -553,8 +646,14 @@
       <c r="C14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>44940</v>
       </c>
@@ -564,8 +663,14 @@
       <c r="C15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>44941</v>
       </c>
@@ -575,8 +680,14 @@
       <c r="C16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>44942</v>
       </c>
@@ -586,8 +697,14 @@
       <c r="C17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>44943</v>
       </c>
@@ -597,8 +714,14 @@
       <c r="C18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>44944</v>
       </c>
@@ -608,8 +731,14 @@
       <c r="C19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>44945</v>
       </c>
@@ -619,8 +748,14 @@
       <c r="C20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>44946</v>
       </c>
@@ -630,8 +765,14 @@
       <c r="C21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>44947</v>
       </c>
@@ -641,8 +782,14 @@
       <c r="C22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>44948</v>
       </c>
@@ -652,8 +799,14 @@
       <c r="C23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>44949</v>
       </c>
@@ -663,8 +816,14 @@
       <c r="C24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>44950</v>
       </c>
@@ -674,8 +833,14 @@
       <c r="C25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>44951</v>
       </c>
@@ -685,8 +850,14 @@
       <c r="C26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>44952</v>
       </c>
@@ -696,8 +867,14 @@
       <c r="C27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>44953</v>
       </c>
@@ -707,8 +884,14 @@
       <c r="C28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>44954</v>
       </c>
@@ -718,8 +901,14 @@
       <c r="C29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>44955</v>
       </c>
@@ -729,8 +918,14 @@
       <c r="C30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>44956</v>
       </c>
@@ -740,8 +935,14 @@
       <c r="C31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>44957</v>
       </c>
@@ -751,8 +952,14 @@
       <c r="C32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>44958</v>
       </c>
@@ -762,8 +969,14 @@
       <c r="C33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>44959</v>
       </c>
@@ -773,8 +986,14 @@
       <c r="C34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>44960</v>
       </c>
@@ -784,8 +1003,14 @@
       <c r="C35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>44961</v>
       </c>
@@ -795,8 +1020,14 @@
       <c r="C36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>44962</v>
       </c>
@@ -806,8 +1037,14 @@
       <c r="C37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>44963</v>
       </c>
@@ -817,8 +1054,14 @@
       <c r="C38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>44964</v>
       </c>
@@ -828,8 +1071,14 @@
       <c r="C39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>44965</v>
       </c>
@@ -839,8 +1088,14 @@
       <c r="C40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>44966</v>
       </c>
@@ -850,8 +1105,14 @@
       <c r="C41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>44967</v>
       </c>
@@ -861,8 +1122,14 @@
       <c r="C42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>44968</v>
       </c>
@@ -872,8 +1139,14 @@
       <c r="C43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>44969</v>
       </c>
@@ -883,8 +1156,14 @@
       <c r="C44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44970</v>
       </c>
@@ -894,8 +1173,14 @@
       <c r="C45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>44971</v>
       </c>
@@ -905,8 +1190,14 @@
       <c r="C46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>44972</v>
       </c>
@@ -916,8 +1207,14 @@
       <c r="C47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>44973</v>
       </c>
@@ -927,8 +1224,14 @@
       <c r="C48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>44974</v>
       </c>
@@ -938,8 +1241,14 @@
       <c r="C49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>44975</v>
       </c>
@@ -949,8 +1258,14 @@
       <c r="C50">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>44976</v>
       </c>
@@ -960,8 +1275,14 @@
       <c r="C51">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>44977</v>
       </c>
@@ -971,8 +1292,14 @@
       <c r="C52">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>44978</v>
       </c>
@@ -982,8 +1309,14 @@
       <c r="C53">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>44979</v>
       </c>
@@ -993,8 +1326,14 @@
       <c r="C54">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>44980</v>
       </c>
@@ -1004,8 +1343,14 @@
       <c r="C55">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>44981</v>
       </c>
@@ -1015,8 +1360,14 @@
       <c r="C56">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>44982</v>
       </c>
@@ -1026,8 +1377,14 @@
       <c r="C57">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>44983</v>
       </c>
@@ -1037,8 +1394,14 @@
       <c r="C58">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>44984</v>
       </c>
@@ -1048,8 +1411,14 @@
       <c r="C59">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>44985</v>
       </c>
@@ -1059,8 +1428,14 @@
       <c r="C60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>44986</v>
       </c>
@@ -1070,8 +1445,14 @@
       <c r="C61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>44987</v>
       </c>
@@ -1081,8 +1462,14 @@
       <c r="C62">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>44988</v>
       </c>
@@ -1092,8 +1479,14 @@
       <c r="C63">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>44989</v>
       </c>
@@ -1103,8 +1496,14 @@
       <c r="C64">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>44990</v>
       </c>
@@ -1114,8 +1513,14 @@
       <c r="C65">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>44991</v>
       </c>
@@ -1125,8 +1530,14 @@
       <c r="C66">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>44992</v>
       </c>
@@ -1136,8 +1547,14 @@
       <c r="C67">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>44993</v>
       </c>
@@ -1147,8 +1564,14 @@
       <c r="C68">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>44994</v>
       </c>
@@ -1158,8 +1581,14 @@
       <c r="C69">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>44995</v>
       </c>
@@ -1169,8 +1598,14 @@
       <c r="C70">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>44996</v>
       </c>
@@ -1180,8 +1615,14 @@
       <c r="C71">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>44997</v>
       </c>
@@ -1191,8 +1632,14 @@
       <c r="C72">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>44998</v>
       </c>
@@ -1202,8 +1649,14 @@
       <c r="C73">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>44999</v>
       </c>
@@ -1213,8 +1666,14 @@
       <c r="C74">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>45000</v>
       </c>
@@ -1224,8 +1683,14 @@
       <c r="C75">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>45001</v>
       </c>
@@ -1235,8 +1700,14 @@
       <c r="C76">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>45002</v>
       </c>
@@ -1246,8 +1717,14 @@
       <c r="C77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>45003</v>
       </c>
@@ -1257,8 +1734,14 @@
       <c r="C78">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>45004</v>
       </c>
@@ -1268,8 +1751,14 @@
       <c r="C79">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>45005</v>
       </c>
@@ -1279,8 +1768,14 @@
       <c r="C80">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>45006</v>
       </c>
@@ -1290,8 +1785,14 @@
       <c r="C81">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>45007</v>
       </c>
@@ -1301,8 +1802,14 @@
       <c r="C82">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>45008</v>
       </c>
@@ -1312,8 +1819,14 @@
       <c r="C83">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>45009</v>
       </c>
@@ -1323,8 +1836,14 @@
       <c r="C84">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>45010</v>
       </c>
@@ -1334,8 +1853,14 @@
       <c r="C85">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>45011</v>
       </c>
@@ -1345,8 +1870,14 @@
       <c r="C86">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>45012</v>
       </c>
@@ -1356,8 +1887,14 @@
       <c r="C87">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>45013</v>
       </c>
@@ -1367,8 +1904,14 @@
       <c r="C88">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>45014</v>
       </c>
@@ -1378,8 +1921,14 @@
       <c r="C89">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>45015</v>
       </c>
@@ -1389,8 +1938,14 @@
       <c r="C90">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>45016</v>
       </c>
@@ -1400,8 +1955,14 @@
       <c r="C91">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>45017</v>
       </c>
@@ -1411,8 +1972,14 @@
       <c r="C92">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>45018</v>
       </c>
@@ -1422,8 +1989,14 @@
       <c r="C93">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>45019</v>
       </c>
@@ -1433,8 +2006,14 @@
       <c r="C94">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>45020</v>
       </c>
@@ -1444,8 +2023,14 @@
       <c r="C95">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>45021</v>
       </c>
@@ -1455,8 +2040,14 @@
       <c r="C96">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>45022</v>
       </c>
@@ -1466,8 +2057,14 @@
       <c r="C97">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>45023</v>
       </c>
@@ -1477,8 +2074,14 @@
       <c r="C98">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>45024</v>
       </c>
@@ -1488,8 +2091,14 @@
       <c r="C99">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>45025</v>
       </c>
@@ -1499,8 +2108,14 @@
       <c r="C100">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>45026</v>
       </c>
@@ -1510,8 +2125,14 @@
       <c r="C101">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>45027</v>
       </c>
@@ -1521,8 +2142,14 @@
       <c r="C102">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>45028</v>
       </c>
@@ -1532,8 +2159,14 @@
       <c r="C103">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>45029</v>
       </c>
@@ -1543,8 +2176,14 @@
       <c r="C104">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104">
+        <v>1</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>45030</v>
       </c>
@@ -1554,8 +2193,14 @@
       <c r="C105">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>45031</v>
       </c>
@@ -1565,8 +2210,14 @@
       <c r="C106">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106">
+        <v>1</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>45032</v>
       </c>
@@ -1576,8 +2227,14 @@
       <c r="C107">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>45033</v>
       </c>
@@ -1587,8 +2244,14 @@
       <c r="C108">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108">
+        <v>1</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>45034</v>
       </c>
@@ -1598,8 +2261,14 @@
       <c r="C109">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109">
+        <v>1</v>
+      </c>
+      <c r="E109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>45035</v>
       </c>
@@ -1609,8 +2278,14 @@
       <c r="C110">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110">
+        <v>1</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>45036</v>
       </c>
@@ -1620,8 +2295,14 @@
       <c r="C111">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111">
+        <v>1</v>
+      </c>
+      <c r="E111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>45037</v>
       </c>
@@ -1631,8 +2312,14 @@
       <c r="C112">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112">
+        <v>1</v>
+      </c>
+      <c r="E112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>45038</v>
       </c>
@@ -1642,8 +2329,14 @@
       <c r="C113">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113">
+        <v>1</v>
+      </c>
+      <c r="E113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>45039</v>
       </c>
@@ -1653,8 +2346,14 @@
       <c r="C114">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114">
+        <v>1</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>45040</v>
       </c>
@@ -1664,8 +2363,14 @@
       <c r="C115">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115">
+        <v>1</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>45041</v>
       </c>
@@ -1675,8 +2380,14 @@
       <c r="C116">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116">
+        <v>1</v>
+      </c>
+      <c r="E116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>45042</v>
       </c>
@@ -1686,8 +2397,14 @@
       <c r="C117">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117">
+        <v>1</v>
+      </c>
+      <c r="E117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>45043</v>
       </c>
@@ -1697,8 +2414,14 @@
       <c r="C118">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118">
+        <v>1</v>
+      </c>
+      <c r="E118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>45044</v>
       </c>
@@ -1708,8 +2431,14 @@
       <c r="C119">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119">
+        <v>1</v>
+      </c>
+      <c r="E119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>45045</v>
       </c>
@@ -1719,8 +2448,14 @@
       <c r="C120">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="E120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>45046</v>
       </c>
@@ -1730,8 +2465,14 @@
       <c r="C121">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121">
+        <v>1</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>45047</v>
       </c>
@@ -1741,8 +2482,14 @@
       <c r="C122">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122">
+        <v>1</v>
+      </c>
+      <c r="E122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>45048</v>
       </c>
@@ -1752,8 +2499,14 @@
       <c r="C123">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123">
+        <v>1</v>
+      </c>
+      <c r="E123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>45049</v>
       </c>
@@ -1763,8 +2516,14 @@
       <c r="C124">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124">
+        <v>1</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>45050</v>
       </c>
@@ -1774,8 +2533,14 @@
       <c r="C125">
         <v>1</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125">
+        <v>1</v>
+      </c>
+      <c r="E125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>45051</v>
       </c>
@@ -1785,8 +2550,14 @@
       <c r="C126">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126">
+        <v>1</v>
+      </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>45052</v>
       </c>
@@ -1796,8 +2567,14 @@
       <c r="C127">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127">
+        <v>1</v>
+      </c>
+      <c r="E127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>45053</v>
       </c>
@@ -1807,8 +2584,14 @@
       <c r="C128">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128">
+        <v>1</v>
+      </c>
+      <c r="E128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>45054</v>
       </c>
@@ -1818,8 +2601,14 @@
       <c r="C129">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="E129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>45055</v>
       </c>
@@ -1829,8 +2618,14 @@
       <c r="C130">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130">
+        <v>1</v>
+      </c>
+      <c r="E130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>45056</v>
       </c>
@@ -1840,8 +2635,14 @@
       <c r="C131">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131">
+        <v>1</v>
+      </c>
+      <c r="E131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>45057</v>
       </c>
@@ -1851,8 +2652,14 @@
       <c r="C132">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132">
+        <v>1</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>45058</v>
       </c>
@@ -1862,8 +2669,14 @@
       <c r="C133">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133">
+        <v>1</v>
+      </c>
+      <c r="E133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>45059</v>
       </c>
@@ -1873,8 +2686,14 @@
       <c r="C134">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>45060</v>
       </c>
@@ -1884,8 +2703,14 @@
       <c r="C135">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135">
+        <v>1</v>
+      </c>
+      <c r="E135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>45061</v>
       </c>
@@ -1895,8 +2720,14 @@
       <c r="C136">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>45062</v>
       </c>
@@ -1906,8 +2737,14 @@
       <c r="C137">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>45063</v>
       </c>
@@ -1917,8 +2754,14 @@
       <c r="C138">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138">
+        <v>1</v>
+      </c>
+      <c r="E138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>45064</v>
       </c>
@@ -1928,8 +2771,14 @@
       <c r="C139">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139">
+        <v>1</v>
+      </c>
+      <c r="E139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>45065</v>
       </c>
@@ -1939,8 +2788,14 @@
       <c r="C140">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140">
+        <v>1</v>
+      </c>
+      <c r="E140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>45066</v>
       </c>
@@ -1950,8 +2805,14 @@
       <c r="C141">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141">
+        <v>1</v>
+      </c>
+      <c r="E141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>45067</v>
       </c>
@@ -1961,8 +2822,14 @@
       <c r="C142">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142">
+        <v>1</v>
+      </c>
+      <c r="E142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>45068</v>
       </c>
@@ -1972,8 +2839,14 @@
       <c r="C143">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143">
+        <v>1</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>45069</v>
       </c>
@@ -1983,8 +2856,14 @@
       <c r="C144">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144">
+        <v>1</v>
+      </c>
+      <c r="E144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>45070</v>
       </c>
@@ -1994,8 +2873,14 @@
       <c r="C145">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145">
+        <v>1</v>
+      </c>
+      <c r="E145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>45071</v>
       </c>
@@ -2005,8 +2890,14 @@
       <c r="C146">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146">
+        <v>1</v>
+      </c>
+      <c r="E146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>45072</v>
       </c>
@@ -2016,8 +2907,14 @@
       <c r="C147">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147">
+        <v>1</v>
+      </c>
+      <c r="E147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>45073</v>
       </c>
@@ -2027,8 +2924,14 @@
       <c r="C148">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148">
+        <v>1</v>
+      </c>
+      <c r="E148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>45074</v>
       </c>
@@ -2038,8 +2941,14 @@
       <c r="C149">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149">
+        <v>1</v>
+      </c>
+      <c r="E149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>45075</v>
       </c>
@@ -2049,8 +2958,14 @@
       <c r="C150">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150">
+        <v>1</v>
+      </c>
+      <c r="E150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>45076</v>
       </c>
@@ -2060,8 +2975,14 @@
       <c r="C151">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151">
+        <v>1</v>
+      </c>
+      <c r="E151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>45077</v>
       </c>
@@ -2071,8 +2992,14 @@
       <c r="C152">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152">
+        <v>1</v>
+      </c>
+      <c r="E152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>45078</v>
       </c>
@@ -2082,8 +3009,14 @@
       <c r="C153">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153">
+        <v>1</v>
+      </c>
+      <c r="E153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>45079</v>
       </c>
@@ -2093,8 +3026,14 @@
       <c r="C154">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D154">
+        <v>1</v>
+      </c>
+      <c r="E154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>45080</v>
       </c>
@@ -2104,8 +3043,14 @@
       <c r="C155">
         <v>1</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D155">
+        <v>1</v>
+      </c>
+      <c r="E155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>45081</v>
       </c>
@@ -2115,8 +3060,14 @@
       <c r="C156">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D156">
+        <v>1</v>
+      </c>
+      <c r="E156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>45082</v>
       </c>
@@ -2126,8 +3077,14 @@
       <c r="C157">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D157">
+        <v>1</v>
+      </c>
+      <c r="E157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>45083</v>
       </c>
@@ -2137,8 +3094,14 @@
       <c r="C158">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158">
+        <v>1</v>
+      </c>
+      <c r="E158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>45084</v>
       </c>
@@ -2148,8 +3111,14 @@
       <c r="C159">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159">
+        <v>1</v>
+      </c>
+      <c r="E159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>45085</v>
       </c>
@@ -2159,8 +3128,14 @@
       <c r="C160">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160">
+        <v>1</v>
+      </c>
+      <c r="E160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>45086</v>
       </c>
@@ -2170,8 +3145,14 @@
       <c r="C161">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161">
+        <v>1</v>
+      </c>
+      <c r="E161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>45087</v>
       </c>
@@ -2181,8 +3162,14 @@
       <c r="C162">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162">
+        <v>1</v>
+      </c>
+      <c r="E162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>45088</v>
       </c>
@@ -2192,8 +3179,14 @@
       <c r="C163">
         <v>1</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163">
+        <v>1</v>
+      </c>
+      <c r="E163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>45089</v>
       </c>
@@ -2203,8 +3196,14 @@
       <c r="C164">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164">
+        <v>1</v>
+      </c>
+      <c r="E164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>45090</v>
       </c>
@@ -2214,8 +3213,14 @@
       <c r="C165">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165">
+        <v>1</v>
+      </c>
+      <c r="E165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>45091</v>
       </c>
@@ -2225,8 +3230,14 @@
       <c r="C166">
         <v>1</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D166">
+        <v>1</v>
+      </c>
+      <c r="E166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>45092</v>
       </c>
@@ -2236,8 +3247,14 @@
       <c r="C167">
         <v>1</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D167">
+        <v>1</v>
+      </c>
+      <c r="E167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>45093</v>
       </c>
@@ -2247,8 +3264,14 @@
       <c r="C168">
         <v>1</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D168">
+        <v>1</v>
+      </c>
+      <c r="E168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>45094</v>
       </c>
@@ -2258,8 +3281,14 @@
       <c r="C169">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D169">
+        <v>1</v>
+      </c>
+      <c r="E169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>45095</v>
       </c>
@@ -2269,8 +3298,14 @@
       <c r="C170">
         <v>1</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D170">
+        <v>1</v>
+      </c>
+      <c r="E170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>45096</v>
       </c>
@@ -2280,8 +3315,14 @@
       <c r="C171">
         <v>1</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D171">
+        <v>1</v>
+      </c>
+      <c r="E171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>45097</v>
       </c>
@@ -2291,8 +3332,14 @@
       <c r="C172">
         <v>1</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D172">
+        <v>1</v>
+      </c>
+      <c r="E172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>45098</v>
       </c>
@@ -2302,8 +3349,14 @@
       <c r="C173">
         <v>1</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D173">
+        <v>1</v>
+      </c>
+      <c r="E173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>45099</v>
       </c>
@@ -2313,8 +3366,14 @@
       <c r="C174">
         <v>1</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D174">
+        <v>1</v>
+      </c>
+      <c r="E174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>45100</v>
       </c>
@@ -2324,8 +3383,14 @@
       <c r="C175">
         <v>1</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D175">
+        <v>1</v>
+      </c>
+      <c r="E175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>45101</v>
       </c>
@@ -2335,8 +3400,14 @@
       <c r="C176">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D176">
+        <v>1</v>
+      </c>
+      <c r="E176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>45102</v>
       </c>
@@ -2346,8 +3417,14 @@
       <c r="C177">
         <v>1</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D177">
+        <v>1</v>
+      </c>
+      <c r="E177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>45103</v>
       </c>
@@ -2357,8 +3434,14 @@
       <c r="C178">
         <v>1</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D178">
+        <v>1</v>
+      </c>
+      <c r="E178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>45104</v>
       </c>
@@ -2368,8 +3451,14 @@
       <c r="C179">
         <v>1</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D179">
+        <v>1</v>
+      </c>
+      <c r="E179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>45105</v>
       </c>
@@ -2379,8 +3468,14 @@
       <c r="C180">
         <v>1</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D180">
+        <v>1</v>
+      </c>
+      <c r="E180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>45106</v>
       </c>
@@ -2390,8 +3485,14 @@
       <c r="C181">
         <v>1</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D181">
+        <v>1</v>
+      </c>
+      <c r="E181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>45107</v>
       </c>
@@ -2401,8 +3502,14 @@
       <c r="C182">
         <v>1</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D182">
+        <v>1</v>
+      </c>
+      <c r="E182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>45108</v>
       </c>
@@ -2412,8 +3519,14 @@
       <c r="C183">
         <v>1</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D183">
+        <v>1</v>
+      </c>
+      <c r="E183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>45109</v>
       </c>
@@ -2423,8 +3536,14 @@
       <c r="C184">
         <v>1</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D184">
+        <v>1</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>45110</v>
       </c>
@@ -2434,8 +3553,14 @@
       <c r="C185">
         <v>1</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D185">
+        <v>1</v>
+      </c>
+      <c r="E185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>45111</v>
       </c>
@@ -2445,8 +3570,14 @@
       <c r="C186">
         <v>1</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D186">
+        <v>1</v>
+      </c>
+      <c r="E186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>45112</v>
       </c>
@@ -2456,8 +3587,14 @@
       <c r="C187">
         <v>1</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D187">
+        <v>1</v>
+      </c>
+      <c r="E187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>45113</v>
       </c>
@@ -2467,8 +3604,14 @@
       <c r="C188">
         <v>1</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D188">
+        <v>1</v>
+      </c>
+      <c r="E188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>45114</v>
       </c>
@@ -2478,8 +3621,14 @@
       <c r="C189">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D189">
+        <v>1</v>
+      </c>
+      <c r="E189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>45115</v>
       </c>
@@ -2489,8 +3638,14 @@
       <c r="C190">
         <v>1</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D190">
+        <v>1</v>
+      </c>
+      <c r="E190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>45116</v>
       </c>
@@ -2500,8 +3655,14 @@
       <c r="C191">
         <v>1</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D191">
+        <v>1</v>
+      </c>
+      <c r="E191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>45117</v>
       </c>
@@ -2511,8 +3672,14 @@
       <c r="C192">
         <v>1</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D192">
+        <v>1</v>
+      </c>
+      <c r="E192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>45118</v>
       </c>
@@ -2522,8 +3689,14 @@
       <c r="C193">
         <v>1</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D193">
+        <v>1</v>
+      </c>
+      <c r="E193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>45119</v>
       </c>
@@ -2533,8 +3706,14 @@
       <c r="C194">
         <v>1</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>45120</v>
       </c>
@@ -2544,8 +3723,14 @@
       <c r="C195">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D195">
+        <v>1</v>
+      </c>
+      <c r="E195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>45121</v>
       </c>
@@ -2555,8 +3740,14 @@
       <c r="C196">
         <v>1</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D196">
+        <v>1</v>
+      </c>
+      <c r="E196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>45122</v>
       </c>
@@ -2566,8 +3757,14 @@
       <c r="C197">
         <v>1</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D197">
+        <v>1</v>
+      </c>
+      <c r="E197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>45123</v>
       </c>
@@ -2577,8 +3774,14 @@
       <c r="C198">
         <v>1</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D198">
+        <v>1</v>
+      </c>
+      <c r="E198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>45124</v>
       </c>
@@ -2588,8 +3791,14 @@
       <c r="C199">
         <v>1</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D199">
+        <v>1</v>
+      </c>
+      <c r="E199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>45125</v>
       </c>
@@ -2599,8 +3808,14 @@
       <c r="C200">
         <v>1</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D200">
+        <v>1</v>
+      </c>
+      <c r="E200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>45126</v>
       </c>
@@ -2610,8 +3825,14 @@
       <c r="C201">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D201">
+        <v>1</v>
+      </c>
+      <c r="E201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>45127</v>
       </c>
@@ -2621,8 +3842,14 @@
       <c r="C202">
         <v>1</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D202">
+        <v>1</v>
+      </c>
+      <c r="E202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>45128</v>
       </c>
@@ -2632,8 +3859,14 @@
       <c r="C203">
         <v>1</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D203">
+        <v>1</v>
+      </c>
+      <c r="E203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>45129</v>
       </c>
@@ -2643,8 +3876,14 @@
       <c r="C204">
         <v>1</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D204">
+        <v>1</v>
+      </c>
+      <c r="E204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>45130</v>
       </c>
@@ -2654,8 +3893,14 @@
       <c r="C205">
         <v>1</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D205">
+        <v>1</v>
+      </c>
+      <c r="E205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>45131</v>
       </c>
@@ -2665,8 +3910,14 @@
       <c r="C206">
         <v>1</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D206">
+        <v>1</v>
+      </c>
+      <c r="E206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>45132</v>
       </c>
@@ -2676,8 +3927,14 @@
       <c r="C207">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D207">
+        <v>1</v>
+      </c>
+      <c r="E207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>45133</v>
       </c>
@@ -2687,8 +3944,14 @@
       <c r="C208">
         <v>1</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D208">
+        <v>1</v>
+      </c>
+      <c r="E208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>45134</v>
       </c>
@@ -2698,8 +3961,14 @@
       <c r="C209">
         <v>1</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D209">
+        <v>1</v>
+      </c>
+      <c r="E209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>45135</v>
       </c>
@@ -2709,8 +3978,14 @@
       <c r="C210">
         <v>1</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D210">
+        <v>1</v>
+      </c>
+      <c r="E210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>45136</v>
       </c>
@@ -2720,8 +3995,14 @@
       <c r="C211">
         <v>1</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D211">
+        <v>1</v>
+      </c>
+      <c r="E211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>45137</v>
       </c>
@@ -2731,8 +4012,14 @@
       <c r="C212">
         <v>1</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D212">
+        <v>1</v>
+      </c>
+      <c r="E212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>45138</v>
       </c>
@@ -2742,8 +4029,14 @@
       <c r="C213">
         <v>1</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D213">
+        <v>1</v>
+      </c>
+      <c r="E213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>45139</v>
       </c>
@@ -2753,8 +4046,14 @@
       <c r="C214">
         <v>1</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D214">
+        <v>1</v>
+      </c>
+      <c r="E214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>45140</v>
       </c>
@@ -2764,8 +4063,14 @@
       <c r="C215">
         <v>1</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D215">
+        <v>1</v>
+      </c>
+      <c r="E215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>45141</v>
       </c>
@@ -2775,8 +4080,14 @@
       <c r="C216">
         <v>1</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D216">
+        <v>1</v>
+      </c>
+      <c r="E216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>45142</v>
       </c>
@@ -2786,8 +4097,14 @@
       <c r="C217">
         <v>1</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D217">
+        <v>1</v>
+      </c>
+      <c r="E217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>45143</v>
       </c>
@@ -2797,8 +4114,14 @@
       <c r="C218">
         <v>1</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D218">
+        <v>1</v>
+      </c>
+      <c r="E218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>45144</v>
       </c>
@@ -2808,8 +4131,14 @@
       <c r="C219">
         <v>1</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D219">
+        <v>1</v>
+      </c>
+      <c r="E219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>45145</v>
       </c>
@@ -2819,8 +4148,14 @@
       <c r="C220">
         <v>1</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D220">
+        <v>1</v>
+      </c>
+      <c r="E220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>45146</v>
       </c>
@@ -2830,8 +4165,14 @@
       <c r="C221">
         <v>1</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D221">
+        <v>1</v>
+      </c>
+      <c r="E221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>45147</v>
       </c>
@@ -2841,8 +4182,14 @@
       <c r="C222">
         <v>1</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D222">
+        <v>1</v>
+      </c>
+      <c r="E222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>45148</v>
       </c>
@@ -2852,8 +4199,14 @@
       <c r="C223">
         <v>1</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D223">
+        <v>1</v>
+      </c>
+      <c r="E223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>45149</v>
       </c>
@@ -2863,8 +4216,14 @@
       <c r="C224">
         <v>1</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D224">
+        <v>1</v>
+      </c>
+      <c r="E224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>45150</v>
       </c>
@@ -2874,8 +4233,14 @@
       <c r="C225">
         <v>1</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D225">
+        <v>1</v>
+      </c>
+      <c r="E225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>45151</v>
       </c>
@@ -2885,8 +4250,14 @@
       <c r="C226">
         <v>1</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D226">
+        <v>1</v>
+      </c>
+      <c r="E226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>45152</v>
       </c>
@@ -2896,8 +4267,14 @@
       <c r="C227">
         <v>1</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D227">
+        <v>1</v>
+      </c>
+      <c r="E227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>45153</v>
       </c>
@@ -2907,8 +4284,14 @@
       <c r="C228">
         <v>1</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D228">
+        <v>1</v>
+      </c>
+      <c r="E228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>45154</v>
       </c>
@@ -2918,8 +4301,14 @@
       <c r="C229">
         <v>1</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D229">
+        <v>1</v>
+      </c>
+      <c r="E229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>45155</v>
       </c>
@@ -2929,8 +4318,14 @@
       <c r="C230">
         <v>1</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D230">
+        <v>1</v>
+      </c>
+      <c r="E230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>45156</v>
       </c>
@@ -2940,8 +4335,14 @@
       <c r="C231">
         <v>1</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D231">
+        <v>1</v>
+      </c>
+      <c r="E231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>45157</v>
       </c>
@@ -2951,8 +4352,14 @@
       <c r="C232">
         <v>1</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D232">
+        <v>1</v>
+      </c>
+      <c r="E232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>45158</v>
       </c>
@@ -2962,8 +4369,14 @@
       <c r="C233">
         <v>1</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D233">
+        <v>1</v>
+      </c>
+      <c r="E233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>45159</v>
       </c>
@@ -2973,8 +4386,14 @@
       <c r="C234">
         <v>1</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D234">
+        <v>1</v>
+      </c>
+      <c r="E234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>45160</v>
       </c>
@@ -2984,8 +4403,14 @@
       <c r="C235">
         <v>1</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D235">
+        <v>1</v>
+      </c>
+      <c r="E235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>45161</v>
       </c>
@@ -2995,8 +4420,14 @@
       <c r="C236">
         <v>1</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D236">
+        <v>1</v>
+      </c>
+      <c r="E236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>45162</v>
       </c>
@@ -3006,8 +4437,14 @@
       <c r="C237">
         <v>1</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D237">
+        <v>1</v>
+      </c>
+      <c r="E237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>45163</v>
       </c>
@@ -3017,8 +4454,14 @@
       <c r="C238">
         <v>1</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D238">
+        <v>1</v>
+      </c>
+      <c r="E238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>45164</v>
       </c>
@@ -3028,8 +4471,14 @@
       <c r="C239">
         <v>1</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D239">
+        <v>1</v>
+      </c>
+      <c r="E239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>45165</v>
       </c>
@@ -3039,8 +4488,14 @@
       <c r="C240">
         <v>1</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D240">
+        <v>1</v>
+      </c>
+      <c r="E240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>45166</v>
       </c>
@@ -3050,8 +4505,14 @@
       <c r="C241">
         <v>1</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D241">
+        <v>1</v>
+      </c>
+      <c r="E241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>45167</v>
       </c>
@@ -3061,8 +4522,14 @@
       <c r="C242">
         <v>1</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D242">
+        <v>1</v>
+      </c>
+      <c r="E242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>45168</v>
       </c>
@@ -3072,8 +4539,14 @@
       <c r="C243">
         <v>1</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D243">
+        <v>1</v>
+      </c>
+      <c r="E243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>45169</v>
       </c>
@@ -3083,8 +4556,14 @@
       <c r="C244">
         <v>1</v>
       </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D244">
+        <v>1</v>
+      </c>
+      <c r="E244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>45170</v>
       </c>
@@ -3094,8 +4573,14 @@
       <c r="C245">
         <v>1</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D245">
+        <v>1</v>
+      </c>
+      <c r="E245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>45171</v>
       </c>
@@ -3105,8 +4590,14 @@
       <c r="C246">
         <v>1</v>
       </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D246">
+        <v>1</v>
+      </c>
+      <c r="E246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>45172</v>
       </c>
@@ -3116,8 +4607,14 @@
       <c r="C247">
         <v>1</v>
       </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D247">
+        <v>1</v>
+      </c>
+      <c r="E247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>45173</v>
       </c>
@@ -3127,8 +4624,14 @@
       <c r="C248">
         <v>1</v>
       </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D248">
+        <v>1</v>
+      </c>
+      <c r="E248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>45174</v>
       </c>
@@ -3138,8 +4641,14 @@
       <c r="C249">
         <v>1</v>
       </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D249">
+        <v>1</v>
+      </c>
+      <c r="E249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>45175</v>
       </c>
@@ -3149,8 +4658,14 @@
       <c r="C250">
         <v>1</v>
       </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D250">
+        <v>1</v>
+      </c>
+      <c r="E250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>45176</v>
       </c>
@@ -3160,8 +4675,14 @@
       <c r="C251">
         <v>1</v>
       </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D251">
+        <v>1</v>
+      </c>
+      <c r="E251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>45177</v>
       </c>
@@ -3171,8 +4692,14 @@
       <c r="C252">
         <v>1</v>
       </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D252">
+        <v>1</v>
+      </c>
+      <c r="E252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>45178</v>
       </c>
@@ -3182,8 +4709,14 @@
       <c r="C253">
         <v>1</v>
       </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D253">
+        <v>1</v>
+      </c>
+      <c r="E253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>45179</v>
       </c>
@@ -3193,8 +4726,14 @@
       <c r="C254">
         <v>1</v>
       </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D254">
+        <v>1</v>
+      </c>
+      <c r="E254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>45180</v>
       </c>
@@ -3204,8 +4743,14 @@
       <c r="C255">
         <v>1</v>
       </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D255">
+        <v>1</v>
+      </c>
+      <c r="E255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>45181</v>
       </c>
@@ -3215,8 +4760,14 @@
       <c r="C256">
         <v>1</v>
       </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D256">
+        <v>1</v>
+      </c>
+      <c r="E256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>45182</v>
       </c>
@@ -3226,8 +4777,14 @@
       <c r="C257">
         <v>1</v>
       </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D257">
+        <v>1</v>
+      </c>
+      <c r="E257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>45183</v>
       </c>
@@ -3237,8 +4794,14 @@
       <c r="C258">
         <v>1</v>
       </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D258">
+        <v>1</v>
+      </c>
+      <c r="E258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>45184</v>
       </c>
@@ -3248,8 +4811,14 @@
       <c r="C259">
         <v>1</v>
       </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D259">
+        <v>1</v>
+      </c>
+      <c r="E259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>45185</v>
       </c>
@@ -3259,8 +4828,14 @@
       <c r="C260">
         <v>1</v>
       </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D260">
+        <v>1</v>
+      </c>
+      <c r="E260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>45186</v>
       </c>
@@ -3270,8 +4845,14 @@
       <c r="C261">
         <v>1</v>
       </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D261">
+        <v>1</v>
+      </c>
+      <c r="E261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>45187</v>
       </c>
@@ -3281,8 +4862,14 @@
       <c r="C262">
         <v>1</v>
       </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D262">
+        <v>1</v>
+      </c>
+      <c r="E262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>45188</v>
       </c>
@@ -3292,8 +4879,14 @@
       <c r="C263">
         <v>1</v>
       </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D263">
+        <v>1</v>
+      </c>
+      <c r="E263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>45189</v>
       </c>
@@ -3303,8 +4896,14 @@
       <c r="C264">
         <v>1</v>
       </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D264">
+        <v>1</v>
+      </c>
+      <c r="E264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
         <v>45190</v>
       </c>
@@ -3314,8 +4913,14 @@
       <c r="C265">
         <v>1</v>
       </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D265">
+        <v>1</v>
+      </c>
+      <c r="E265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>45191</v>
       </c>
@@ -3325,8 +4930,14 @@
       <c r="C266">
         <v>1</v>
       </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D266">
+        <v>1</v>
+      </c>
+      <c r="E266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <v>45192</v>
       </c>
@@ -3336,8 +4947,14 @@
       <c r="C267">
         <v>1</v>
       </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D267">
+        <v>1</v>
+      </c>
+      <c r="E267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>45193</v>
       </c>
@@ -3347,8 +4964,14 @@
       <c r="C268">
         <v>1</v>
       </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D268">
+        <v>1</v>
+      </c>
+      <c r="E268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>45194</v>
       </c>
@@ -3358,8 +4981,14 @@
       <c r="C269">
         <v>1</v>
       </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D269">
+        <v>1</v>
+      </c>
+      <c r="E269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>45195</v>
       </c>
@@ -3369,8 +4998,14 @@
       <c r="C270">
         <v>1</v>
       </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D270">
+        <v>1</v>
+      </c>
+      <c r="E270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>45196</v>
       </c>
@@ -3380,8 +5015,14 @@
       <c r="C271">
         <v>1</v>
       </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D271">
+        <v>1</v>
+      </c>
+      <c r="E271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>45197</v>
       </c>
@@ -3391,8 +5032,14 @@
       <c r="C272">
         <v>1</v>
       </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D272">
+        <v>1</v>
+      </c>
+      <c r="E272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>45198</v>
       </c>
@@ -3402,8 +5049,14 @@
       <c r="C273">
         <v>1</v>
       </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D273">
+        <v>1</v>
+      </c>
+      <c r="E273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>45199</v>
       </c>
@@ -3413,8 +5066,14 @@
       <c r="C274">
         <v>1</v>
       </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D274">
+        <v>1</v>
+      </c>
+      <c r="E274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>45200</v>
       </c>
@@ -3424,8 +5083,14 @@
       <c r="C275">
         <v>1</v>
       </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D275">
+        <v>1</v>
+      </c>
+      <c r="E275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>45201</v>
       </c>
@@ -3435,8 +5100,14 @@
       <c r="C276">
         <v>1</v>
       </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D276">
+        <v>1</v>
+      </c>
+      <c r="E276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>45202</v>
       </c>
@@ -3446,8 +5117,14 @@
       <c r="C277">
         <v>1</v>
       </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D277">
+        <v>1</v>
+      </c>
+      <c r="E277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>45203</v>
       </c>
@@ -3457,8 +5134,14 @@
       <c r="C278">
         <v>1</v>
       </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D278">
+        <v>1</v>
+      </c>
+      <c r="E278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>45204</v>
       </c>
@@ -3468,8 +5151,14 @@
       <c r="C279">
         <v>1</v>
       </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D279">
+        <v>1</v>
+      </c>
+      <c r="E279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>45205</v>
       </c>
@@ -3479,8 +5168,14 @@
       <c r="C280">
         <v>1</v>
       </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D280">
+        <v>1</v>
+      </c>
+      <c r="E280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>45206</v>
       </c>
@@ -3490,8 +5185,14 @@
       <c r="C281">
         <v>1</v>
       </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D281">
+        <v>1</v>
+      </c>
+      <c r="E281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>45207</v>
       </c>
@@ -3501,8 +5202,14 @@
       <c r="C282">
         <v>1</v>
       </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D282">
+        <v>1</v>
+      </c>
+      <c r="E282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>45208</v>
       </c>
@@ -3512,8 +5219,14 @@
       <c r="C283">
         <v>1</v>
       </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D283">
+        <v>1</v>
+      </c>
+      <c r="E283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>45209</v>
       </c>
@@ -3523,8 +5236,14 @@
       <c r="C284">
         <v>1</v>
       </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D284">
+        <v>1</v>
+      </c>
+      <c r="E284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>45210</v>
       </c>
@@ -3534,8 +5253,14 @@
       <c r="C285">
         <v>1</v>
       </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D285">
+        <v>1</v>
+      </c>
+      <c r="E285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>45211</v>
       </c>
@@ -3545,8 +5270,14 @@
       <c r="C286">
         <v>1</v>
       </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D286">
+        <v>1</v>
+      </c>
+      <c r="E286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>45212</v>
       </c>
@@ -3556,8 +5287,14 @@
       <c r="C287">
         <v>1</v>
       </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D287">
+        <v>1</v>
+      </c>
+      <c r="E287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>45213</v>
       </c>
@@ -3567,8 +5304,14 @@
       <c r="C288">
         <v>1</v>
       </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D288">
+        <v>1</v>
+      </c>
+      <c r="E288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <v>45214</v>
       </c>
@@ -3578,8 +5321,14 @@
       <c r="C289">
         <v>1</v>
       </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D289">
+        <v>1</v>
+      </c>
+      <c r="E289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>45215</v>
       </c>
@@ -3589,8 +5338,14 @@
       <c r="C290">
         <v>1</v>
       </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <v>45216</v>
       </c>
@@ -3600,8 +5355,14 @@
       <c r="C291">
         <v>1</v>
       </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D291">
+        <v>1</v>
+      </c>
+      <c r="E291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <v>45217</v>
       </c>
@@ -3611,8 +5372,14 @@
       <c r="C292">
         <v>1</v>
       </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D292">
+        <v>1</v>
+      </c>
+      <c r="E292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <v>45218</v>
       </c>
@@ -3622,8 +5389,14 @@
       <c r="C293">
         <v>1</v>
       </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D293">
+        <v>1</v>
+      </c>
+      <c r="E293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>45219</v>
       </c>
@@ -3633,8 +5406,14 @@
       <c r="C294">
         <v>1</v>
       </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D294">
+        <v>1</v>
+      </c>
+      <c r="E294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
         <v>45220</v>
       </c>
@@ -3644,8 +5423,14 @@
       <c r="C295">
         <v>1</v>
       </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D295">
+        <v>1</v>
+      </c>
+      <c r="E295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <v>45221</v>
       </c>
@@ -3655,8 +5440,14 @@
       <c r="C296">
         <v>1</v>
       </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D296">
+        <v>1</v>
+      </c>
+      <c r="E296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <v>45222</v>
       </c>
@@ -3666,8 +5457,14 @@
       <c r="C297">
         <v>1</v>
       </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D297">
+        <v>1</v>
+      </c>
+      <c r="E297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>45223</v>
       </c>
@@ -3677,8 +5474,14 @@
       <c r="C298">
         <v>1</v>
       </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D298">
+        <v>1</v>
+      </c>
+      <c r="E298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <v>45224</v>
       </c>
@@ -3688,8 +5491,14 @@
       <c r="C299">
         <v>1</v>
       </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D299">
+        <v>1</v>
+      </c>
+      <c r="E299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
         <v>45225</v>
       </c>
@@ -3699,8 +5508,14 @@
       <c r="C300">
         <v>1</v>
       </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D300">
+        <v>1</v>
+      </c>
+      <c r="E300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
         <v>45226</v>
       </c>
@@ -3710,8 +5525,14 @@
       <c r="C301">
         <v>1</v>
       </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D301">
+        <v>1</v>
+      </c>
+      <c r="E301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <v>45227</v>
       </c>
@@ -3721,8 +5542,14 @@
       <c r="C302">
         <v>1</v>
       </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D302">
+        <v>1</v>
+      </c>
+      <c r="E302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="2">
         <v>45228</v>
       </c>
@@ -3732,8 +5559,14 @@
       <c r="C303">
         <v>1</v>
       </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D303">
+        <v>1</v>
+      </c>
+      <c r="E303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
         <v>45229</v>
       </c>
@@ -3743,8 +5576,14 @@
       <c r="C304">
         <v>1</v>
       </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D304">
+        <v>1</v>
+      </c>
+      <c r="E304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
         <v>45230</v>
       </c>
@@ -3754,8 +5593,14 @@
       <c r="C305">
         <v>1</v>
       </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D305">
+        <v>1</v>
+      </c>
+      <c r="E305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>45231</v>
       </c>
@@ -3765,8 +5610,14 @@
       <c r="C306">
         <v>1</v>
       </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D306">
+        <v>1</v>
+      </c>
+      <c r="E306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
         <v>45232</v>
       </c>
@@ -3776,8 +5627,14 @@
       <c r="C307">
         <v>1</v>
       </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D307">
+        <v>1</v>
+      </c>
+      <c r="E307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
         <v>45233</v>
       </c>
@@ -3787,8 +5644,14 @@
       <c r="C308">
         <v>1</v>
       </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D308">
+        <v>1</v>
+      </c>
+      <c r="E308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
         <v>45234</v>
       </c>
@@ -3798,8 +5661,14 @@
       <c r="C309">
         <v>1</v>
       </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D309">
+        <v>1</v>
+      </c>
+      <c r="E309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
         <v>45235</v>
       </c>
@@ -3809,8 +5678,14 @@
       <c r="C310">
         <v>1</v>
       </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D310">
+        <v>1</v>
+      </c>
+      <c r="E310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="2">
         <v>45236</v>
       </c>
@@ -3820,8 +5695,14 @@
       <c r="C311">
         <v>1</v>
       </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D311">
+        <v>1</v>
+      </c>
+      <c r="E311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
         <v>45237</v>
       </c>
@@ -3831,8 +5712,14 @@
       <c r="C312">
         <v>1</v>
       </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D312">
+        <v>1</v>
+      </c>
+      <c r="E312">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
         <v>45238</v>
       </c>
@@ -3842,8 +5729,14 @@
       <c r="C313">
         <v>1</v>
       </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D313">
+        <v>1</v>
+      </c>
+      <c r="E313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="2">
         <v>45239</v>
       </c>
@@ -3853,8 +5746,14 @@
       <c r="C314">
         <v>1</v>
       </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D314">
+        <v>1</v>
+      </c>
+      <c r="E314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="2">
         <v>45240</v>
       </c>
@@ -3864,8 +5763,14 @@
       <c r="C315">
         <v>1</v>
       </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D315">
+        <v>1</v>
+      </c>
+      <c r="E315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="2">
         <v>45241</v>
       </c>
@@ -3875,8 +5780,14 @@
       <c r="C316">
         <v>1</v>
       </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D316">
+        <v>1</v>
+      </c>
+      <c r="E316">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="2">
         <v>45242</v>
       </c>
@@ -3886,8 +5797,14 @@
       <c r="C317">
         <v>1</v>
       </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D317">
+        <v>1</v>
+      </c>
+      <c r="E317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="2">
         <v>45243</v>
       </c>
@@ -3897,8 +5814,14 @@
       <c r="C318">
         <v>1</v>
       </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D318">
+        <v>1</v>
+      </c>
+      <c r="E318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="2">
         <v>45244</v>
       </c>
@@ -3908,8 +5831,14 @@
       <c r="C319">
         <v>1</v>
       </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D319">
+        <v>1</v>
+      </c>
+      <c r="E319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="2">
         <v>45245</v>
       </c>
@@ -3919,8 +5848,14 @@
       <c r="C320">
         <v>1</v>
       </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D320">
+        <v>1</v>
+      </c>
+      <c r="E320">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="2">
         <v>45246</v>
       </c>
@@ -3930,8 +5865,14 @@
       <c r="C321">
         <v>1</v>
       </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D321">
+        <v>1</v>
+      </c>
+      <c r="E321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="2">
         <v>45247</v>
       </c>
@@ -3941,8 +5882,14 @@
       <c r="C322">
         <v>1</v>
       </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D322">
+        <v>1</v>
+      </c>
+      <c r="E322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="2">
         <v>45248</v>
       </c>
@@ -3952,8 +5899,14 @@
       <c r="C323">
         <v>1</v>
       </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D323">
+        <v>1</v>
+      </c>
+      <c r="E323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
         <v>45249</v>
       </c>
@@ -3963,8 +5916,14 @@
       <c r="C324">
         <v>1</v>
       </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D324">
+        <v>1</v>
+      </c>
+      <c r="E324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
         <v>45250</v>
       </c>
@@ -3974,8 +5933,14 @@
       <c r="C325">
         <v>1</v>
       </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D325">
+        <v>1</v>
+      </c>
+      <c r="E325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
         <v>45251</v>
       </c>
@@ -3985,8 +5950,14 @@
       <c r="C326">
         <v>1</v>
       </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D326">
+        <v>1</v>
+      </c>
+      <c r="E326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
         <v>45252</v>
       </c>
@@ -3996,8 +5967,14 @@
       <c r="C327">
         <v>1</v>
       </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D327">
+        <v>1</v>
+      </c>
+      <c r="E327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
         <v>45253</v>
       </c>
@@ -4007,8 +5984,14 @@
       <c r="C328">
         <v>1</v>
       </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D328">
+        <v>1</v>
+      </c>
+      <c r="E328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="2">
         <v>45254</v>
       </c>
@@ -4018,8 +6001,14 @@
       <c r="C329">
         <v>1</v>
       </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D329">
+        <v>1</v>
+      </c>
+      <c r="E329">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="2">
         <v>45255</v>
       </c>
@@ -4029,8 +6018,14 @@
       <c r="C330">
         <v>1</v>
       </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D330">
+        <v>1</v>
+      </c>
+      <c r="E330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="2">
         <v>45256</v>
       </c>
@@ -4040,8 +6035,14 @@
       <c r="C331">
         <v>1</v>
       </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D331">
+        <v>1</v>
+      </c>
+      <c r="E331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="2">
         <v>45257</v>
       </c>
@@ -4051,8 +6052,14 @@
       <c r="C332">
         <v>1</v>
       </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D332">
+        <v>1</v>
+      </c>
+      <c r="E332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="2">
         <v>45258</v>
       </c>
@@ -4062,8 +6069,14 @@
       <c r="C333">
         <v>1</v>
       </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D333">
+        <v>1</v>
+      </c>
+      <c r="E333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="2">
         <v>45259</v>
       </c>
@@ -4073,8 +6086,14 @@
       <c r="C334">
         <v>1</v>
       </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D334">
+        <v>1</v>
+      </c>
+      <c r="E334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="2">
         <v>45260</v>
       </c>
@@ -4084,8 +6103,14 @@
       <c r="C335">
         <v>1</v>
       </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D335">
+        <v>1</v>
+      </c>
+      <c r="E335">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="2">
         <v>45261</v>
       </c>
@@ -4095,8 +6120,14 @@
       <c r="C336">
         <v>1</v>
       </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D336">
+        <v>1</v>
+      </c>
+      <c r="E336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="2">
         <v>45262</v>
       </c>
@@ -4106,8 +6137,14 @@
       <c r="C337">
         <v>1</v>
       </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D337">
+        <v>1</v>
+      </c>
+      <c r="E337">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="2">
         <v>45263</v>
       </c>
@@ -4117,8 +6154,14 @@
       <c r="C338">
         <v>1</v>
       </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D338">
+        <v>1</v>
+      </c>
+      <c r="E338">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="2">
         <v>45264</v>
       </c>
@@ -4128,8 +6171,14 @@
       <c r="C339">
         <v>1</v>
       </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D339">
+        <v>1</v>
+      </c>
+      <c r="E339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" s="2">
         <v>45265</v>
       </c>
@@ -4139,8 +6188,14 @@
       <c r="C340">
         <v>1</v>
       </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D340">
+        <v>1</v>
+      </c>
+      <c r="E340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" s="2">
         <v>45266</v>
       </c>
@@ -4150,8 +6205,14 @@
       <c r="C341">
         <v>1</v>
       </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D341">
+        <v>1</v>
+      </c>
+      <c r="E341">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="2">
         <v>45267</v>
       </c>
@@ -4161,8 +6222,14 @@
       <c r="C342">
         <v>1</v>
       </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D342">
+        <v>1</v>
+      </c>
+      <c r="E342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="2">
         <v>45268</v>
       </c>
@@ -4172,8 +6239,14 @@
       <c r="C343">
         <v>1</v>
       </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D343">
+        <v>1</v>
+      </c>
+      <c r="E343">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" s="2">
         <v>45269</v>
       </c>
@@ -4183,8 +6256,14 @@
       <c r="C344">
         <v>1</v>
       </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D344">
+        <v>1</v>
+      </c>
+      <c r="E344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="2">
         <v>45270</v>
       </c>
@@ -4194,8 +6273,14 @@
       <c r="C345">
         <v>1</v>
       </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D345">
+        <v>1</v>
+      </c>
+      <c r="E345">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="2">
         <v>45271</v>
       </c>
@@ -4205,8 +6290,14 @@
       <c r="C346">
         <v>1</v>
       </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D346">
+        <v>1</v>
+      </c>
+      <c r="E346">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" s="2">
         <v>45272</v>
       </c>
@@ -4216,8 +6307,14 @@
       <c r="C347">
         <v>1</v>
       </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D347">
+        <v>1</v>
+      </c>
+      <c r="E347">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" s="2">
         <v>45273</v>
       </c>
@@ -4227,8 +6324,14 @@
       <c r="C348">
         <v>1</v>
       </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D348">
+        <v>1</v>
+      </c>
+      <c r="E348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="2">
         <v>45274</v>
       </c>
@@ -4238,8 +6341,14 @@
       <c r="C349">
         <v>1</v>
       </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D349">
+        <v>1</v>
+      </c>
+      <c r="E349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" s="2">
         <v>45275</v>
       </c>
@@ -4249,8 +6358,14 @@
       <c r="C350">
         <v>1</v>
       </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D350">
+        <v>1</v>
+      </c>
+      <c r="E350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="2">
         <v>45276</v>
       </c>
@@ -4260,8 +6375,14 @@
       <c r="C351">
         <v>1</v>
       </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D351">
+        <v>1</v>
+      </c>
+      <c r="E351">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="2">
         <v>45277</v>
       </c>
@@ -4271,8 +6392,14 @@
       <c r="C352">
         <v>1</v>
       </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D352">
+        <v>1</v>
+      </c>
+      <c r="E352">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="2">
         <v>45278</v>
       </c>
@@ -4282,8 +6409,14 @@
       <c r="C353">
         <v>1</v>
       </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D353">
+        <v>1</v>
+      </c>
+      <c r="E353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="2">
         <v>45279</v>
       </c>
@@ -4293,8 +6426,14 @@
       <c r="C354">
         <v>1</v>
       </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D354">
+        <v>1</v>
+      </c>
+      <c r="E354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="2">
         <v>45280</v>
       </c>
@@ -4304,8 +6443,14 @@
       <c r="C355">
         <v>1</v>
       </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D355">
+        <v>1</v>
+      </c>
+      <c r="E355">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" s="2">
         <v>45281</v>
       </c>
@@ -4315,8 +6460,14 @@
       <c r="C356">
         <v>1</v>
       </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D356">
+        <v>1</v>
+      </c>
+      <c r="E356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" s="2">
         <v>45282</v>
       </c>
@@ -4326,8 +6477,14 @@
       <c r="C357">
         <v>1</v>
       </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D357">
+        <v>1</v>
+      </c>
+      <c r="E357">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="2">
         <v>45283</v>
       </c>
@@ -4337,8 +6494,14 @@
       <c r="C358">
         <v>1</v>
       </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D358">
+        <v>1</v>
+      </c>
+      <c r="E358">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" s="2">
         <v>45284</v>
       </c>
@@ -4348,8 +6511,14 @@
       <c r="C359">
         <v>1</v>
       </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D359">
+        <v>1</v>
+      </c>
+      <c r="E359">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" s="2">
         <v>45285</v>
       </c>
@@ -4359,8 +6528,14 @@
       <c r="C360">
         <v>1</v>
       </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D360">
+        <v>1</v>
+      </c>
+      <c r="E360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" s="2">
         <v>45286</v>
       </c>
@@ -4370,8 +6545,14 @@
       <c r="C361">
         <v>1</v>
       </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D361">
+        <v>1</v>
+      </c>
+      <c r="E361">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="2">
         <v>45287</v>
       </c>
@@ -4381,8 +6562,14 @@
       <c r="C362">
         <v>1</v>
       </c>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D362">
+        <v>1</v>
+      </c>
+      <c r="E362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="2">
         <v>45288</v>
       </c>
@@ -4392,8 +6579,14 @@
       <c r="C363">
         <v>1</v>
       </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D363">
+        <v>1</v>
+      </c>
+      <c r="E363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="2">
         <v>45289</v>
       </c>
@@ -4403,8 +6596,14 @@
       <c r="C364">
         <v>1</v>
       </c>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D364">
+        <v>1</v>
+      </c>
+      <c r="E364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" s="2">
         <v>45290</v>
       </c>
@@ -4414,8 +6613,14 @@
       <c r="C365">
         <v>1</v>
       </c>
-    </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D365">
+        <v>1</v>
+      </c>
+      <c r="E365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" s="2">
         <v>45291</v>
       </c>
@@ -4423,6 +6628,12 @@
         <v>3.0087279820814949E-2</v>
       </c>
       <c r="C366">
+        <v>1</v>
+      </c>
+      <c r="D366">
+        <v>1</v>
+      </c>
+      <c r="E366">
         <v>1</v>
       </c>
     </row>
